--- a/ROADMAP/Daftar Jadwal MK MTE 2026 .xlsx
+++ b/ROADMAP/Daftar Jadwal MK MTE 2026 .xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA MASTER\1. S2 ADAM\MTE 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA MASTER\S2 ADAM\adamtriwibowo\ROADMAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CE32C0-070A-4084-9426-4EFFBEDC5099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19CD55D0-4031-482A-A69F-41D0B6A84C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{4F7884D6-35AD-4C6B-99F6-86196ECC61EE}"/>
+    <workbookView xWindow="6490" yWindow="300" windowWidth="19200" windowHeight="9970" xr2:uid="{4F7884D6-35AD-4C6B-99F6-86196ECC61EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -397,9 +397,6 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -410,19 +407,22 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -762,41 +762,41 @@
   <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="5"/>
-    <col min="2" max="2" width="10.6328125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.7265625" style="5"/>
-    <col min="6" max="6" width="12.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" style="5"/>
-    <col min="8" max="8" width="50.6328125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="47.81640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" style="4"/>
+    <col min="2" max="2" width="10.6328125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="14.36328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.7265625" style="4"/>
+    <col min="6" max="6" width="12.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" style="4"/>
+    <col min="8" max="8" width="50.6328125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="47.81640625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
@@ -811,10 +811,10 @@
       <c r="D4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="8"/>
+      <c r="F4" s="10"/>
       <c r="G4" s="6" t="s">
         <v>44</v>
       </c>
@@ -826,402 +826,402 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9" ht="32" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>1</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>2</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="48" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="4" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="32" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="4" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="48" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>2</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>3</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="32" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="4" t="s">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="32" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="4" t="s">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="48" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="4" t="s">
+    <row r="12" spans="1:9" ht="32" x14ac:dyDescent="0.35">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="48" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>3</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>3</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="32" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="4" t="s">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="4" t="s">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="4" t="s">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="48" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>4</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>3</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="32" x14ac:dyDescent="0.35">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="4" t="s">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="48" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="4" t="s">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="64" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>5</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="1">
         <v>3</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="64" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="4" t="s">
+    <row r="21" spans="1:9" ht="48" x14ac:dyDescent="0.35">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="48" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>6</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="1">
         <v>3</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="48" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="4" t="s">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="32" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
+      <c r="A24" s="1">
         <v>7</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="1">
         <v>3</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="4" t="s">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="48" x14ac:dyDescent="0.35">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="4" t="s">
+    <row r="26" spans="1:9" ht="32" x14ac:dyDescent="0.35">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="3" t="s">
         <v>37</v>
       </c>
     </row>
